--- a/important_mails_2026-04-14.xlsx
+++ b/important_mails_2026-04-14.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+          <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,159 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+          <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-2198715-0729366
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1917549922685067</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Seller Assistant now available in the UK</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Seller Assistant now available in the UK
+[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
+Dear Seller,
+Managing your business on Amazon just got easier.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) is now available in the UK within Seller Central. This AI-powered assistant helps you find relevant information, access insights, and manage your business more efficiently, directly where you already work.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) provides guidance on our tools, policies, and processes using information available across Seller Central, along with personalized responses based on your account data. This allows you to quickly surface insights related to your business performance, inventory planning, listing, compliance, and account health without navigating multiple pages.
+[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-l</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+You recently received a notice about the removal of your listing(s) for the product(s) listed below.
+You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 03/13/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
+For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
+SPC-USAmazon-862019321040611</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -540,39 +688,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -584,39 +732,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -639,39 +787,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -695,39 +843,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -742,39 +890,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -788,39 +936,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -838,40 +986,40 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -889,39 +1037,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -941,39 +1089,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -994,39 +1142,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -1047,40 +1195,40 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -1096,40 +1244,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1147,39 +1295,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -1212,39 +1360,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -1259,39 +1407,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1310,39 +1458,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -1361,39 +1509,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -1405,39 +1553,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -1453,39 +1601,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -1497,39 +1645,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1544,127 +1692,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je creditnota, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je creditnota bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -1680,39 +1740,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -1732,39 +1792,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -1783,39 +1843,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -1824,39 +1884,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1877,39 +1937,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1935,39 +1995,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1987,40 +2047,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2036,39 +2096,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2088,39 +2148,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2146,39 +2206,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2194,39 +2254,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2247,39 +2307,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2293,40 +2353,40 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2343,39 +2403,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2395,39 +2455,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2444,39 +2504,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2499,39 +2559,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2551,39 +2611,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2600,39 +2660,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2649,39 +2709,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2704,39 +2764,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2754,39 +2814,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2804,39 +2864,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2856,39 +2916,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2906,39 +2966,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2956,39 +3016,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3006,39 +3066,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3053,39 +3113,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3103,39 +3163,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3153,39 +3213,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3203,39 +3263,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3250,39 +3310,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3297,39 +3357,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3344,39 +3404,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3395,40 +3455,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3447,39 +3507,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3489,39 +3549,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3539,39 +3599,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3587,39 +3647,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3638,39 +3698,127 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je creditnota, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je creditnota bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3682,39 +3830,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3726,39 +3874,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3770,39 +3918,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -3814,39 +3962,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3858,39 +4006,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -3902,39 +4050,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3946,39 +4094,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3997,39 +4145,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4041,39 +4189,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4085,39 +4233,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4129,39 +4277,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4173,39 +4321,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4217,39 +4365,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4261,39 +4409,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4305,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4356,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4400,40 +4548,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4452,39 +4600,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4496,39 +4644,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4547,39 +4695,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -4611,39 +4759,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -4670,39 +4818,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -4714,39 +4862,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -4756,39 +4904,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -4798,39 +4946,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -4860,39 +5008,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -4910,39 +5058,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4959,39 +5107,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5007,39 +5155,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5068,39 +5216,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5121,39 +5269,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5168,39 +5316,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5214,40 +5362,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5263,39 +5411,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5311,39 +5459,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5359,39 +5507,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5407,40 +5555,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5456,39 +5604,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5506,39 +5654,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5554,39 +5702,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5601,39 +5749,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5648,39 +5796,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5701,40 +5849,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5749,39 +5897,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5802,39 +5950,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -5867,39 +6015,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5915,39 +6063,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5963,39 +6111,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6013,39 +6161,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6062,39 +6210,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -6118,39 +6266,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6165,39 +6313,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6213,39 +6361,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6262,40 +6410,40 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6311,39 +6459,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6356,39 +6504,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6409,39 +6557,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6464,39 +6612,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6517,39 +6665,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6573,39 +6721,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6628,39 +6776,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6678,39 +6826,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6740,39 +6888,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6788,39 +6936,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6836,40 +6984,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6888,40 +7036,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,

--- a/important_mails_2026-04-14.xlsx
+++ b/important_mails_2026-04-14.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -552,21 +552,69 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
+          <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Seller Assistant now available in the UK</t>
+          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
+Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 10/05/2026), we shall dispose of it in accordance with our FBA policies.
+For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
+Thank you for your prompt attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0GKPTF1T7
+ SPC-EUAmazon-510175039347142</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Seller Assistant now available in the UK</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -578,39 +626,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -630,39 +678,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -688,39 +736,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -732,39 +780,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -787,39 +835,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -843,39 +891,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -887,52 +935,6 @@
 Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
  Was this e-mail helpful?
  SPC-EUAmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Nieuregulowane saldo na koncie Amazon</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Witamy!
- Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
- Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
- Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
- Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
- Z poważaniem,
- Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
- Czy ten e-mail był pomocny?
- SPC-EUAmazon-721281267923446</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1848,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>其他风险类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>older</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1861,62 +1863,21 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+          <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Update to FBA item package dimensions</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Update to FBA item package dimensions
- 96
- Starting May 5, 2026, we'll update the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, France, Italy and Spain stores.
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1937,39 +1898,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1995,39 +1956,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2047,40 +2008,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2096,39 +2057,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2148,39 +2109,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2206,39 +2167,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2254,39 +2215,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2307,39 +2268,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2350,6 +2311,52 @@
 Thank you,
 Your Multi-Channel Fulfillment Team
 This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Nieuregulowane saldo na koncie Amazon</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Witamy!
+ Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
+ Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
+ Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
+ Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
+ Z poważaniem,
+ Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
+ Czy ten e-mail był pomocny?
+ SPC-EUAmazon-721281267923446</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3657,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3665,72 +3672,21 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1917550476493542</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3742,39 +3698,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3786,39 +3742,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3830,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -3874,39 +3830,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -3918,39 +3874,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -3962,39 +3918,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4006,39 +3962,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4050,39 +4006,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4094,39 +4050,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4145,39 +4101,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4189,39 +4145,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4233,39 +4189,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4277,39 +4233,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4321,39 +4277,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4365,39 +4321,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4409,39 +4365,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4453,39 +4409,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4504,39 +4460,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4548,40 +4504,40 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4600,39 +4556,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4644,39 +4600,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4695,39 +4651,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -4759,39 +4715,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -4818,39 +4774,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -4862,39 +4818,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -4904,39 +4860,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -4946,39 +4902,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5008,39 +4964,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5058,39 +5014,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5107,39 +5063,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5155,39 +5111,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5216,39 +5172,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5269,39 +5225,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5316,39 +5272,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5362,40 +5318,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5411,39 +5367,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5459,39 +5415,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5507,39 +5463,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5555,40 +5511,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5604,39 +5560,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5654,39 +5610,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5702,39 +5658,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5749,39 +5705,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5796,39 +5752,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5849,40 +5805,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5897,39 +5853,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5950,39 +5906,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6015,39 +5971,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6063,39 +6019,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6111,39 +6067,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6161,39 +6117,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6210,39 +6166,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -6266,232 +6222,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 03/15/26 14:54 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 200,42.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Hola, Weihai EU:
- Para cumplir nuestros requisitos de registro del impuesto sobre el valor añadido (IVA) europeo, necesitamos que nos proporciones más información.
- ¿A qué se debe esto?
- De acuerdo con nuestros requisitos de registro a efectos fiscales en Europa, tienes que proporcionarnos un número de identificación fiscal válido de todos los países en los que consideremos que tienes obligación de registrarte a efectos fiscales o confirmar el estado de registro en la Ventanilla Única del IVA (OSS) en tu país de origen.
- Hemos detectado que tu cuenta tiene que cumplir una serie de requisitos para el registro a efectos fiscales en la Unión Europea, el Reino Unido, Noruega y Suiza, donde tienes la obligación de registrarte a efectos fiscales. En concreto, es posible que tengas que tomar medidas para lo siguiente:
- Polonia
- Para más información, consulta Información sobre el impuesto sobre el valor añadido (IVA) europeo .
- ¿Cómo evito la desactivación de mi cuenta?
- Para evitar la desactivación de la cuenta, consulta la sección "Acciones prioritarias" de la página Estado de la cuenta en los próximos 45 días. Desde ahí podrás hacer lo siguiente:
-- Revisar la información que tienes </t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- potrzebujemy od Ciebie dodatkowych informacji, które pozwolą Ci spełnić europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT.
- Dlaczego tak się stało?
- Zgodnie z europejskimi wymaganiami Amazon dotyczącymi rejestracji jako podatnik VAT musisz podać nam ważny numer VAT dla wszystkich krajów, w których według nas podlegasz obowiązkowi rejestracji jako podatnik VAT, lub potwierdzenie statusu rejestracji w procedurze unijnej w Twoim kraju macierzystym.
- Ustaliliśmy, że w przypadku Twojego konta w Unii Europejskiej, Zjednoczonym Królestwie, Norwegii i Szwajcarii, gdzie masz zobowiązania z tytułu VAT, istnieją wymogi w zakresie rejestracji jako podatnik VAT. Podjęcie działań może być w szczególności wymagane w następujących przypadkach:
- Polska
- Więcej informacji znajdziesz na stronie Informacje dotyczące podatku VAT w Europie .
- Jak mogę zapobiec dezaktywacji konta?
- Aby uniknąć dezaktywacji konta, w ciągu najbliższych 45 dni odwiedź sekcję „Działania priorytetowe” na stronie Kondycja konta . W sekcji tej można:
-- zweryfikować istniejące informacje dotyczące wymienionych krajów
-- przesłać informacje o VAT za pośrednictwem portali „Informacje o</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
- la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Ai fini della conformità ai requisiti di registrazione IVA in Europa di Amazon, ti chiediamo di fornirci ulteriori informazioni.
- Ciò a cosa è dovuto?
- In base ai requisiti di registrazione IVA in Europa di Amazon, sei tenuto a fornirci un numero di partita IVA valido per tutti i paesi in cui riteniamo che tu abbia l'obbligo di effettuare tale registrazione o una conferma dello stato Union One-Stop Shop (OSS) relativo al tuo paese di registrazione.
- Vi sono dei requisiti per la registrazione ai fini IVA che il tuo account deve soddisfare nei paesi in cui sei soggetto a obblighi in materia di IVA (stati dell'Unione europea, Regno Unito, Norvegia e Svizzera). Nello specifico, potrebbe essere necessario un intervento da parte tua per quanto segue:
- Polonia
- Per maggiori informazioni, consulta la pagina di aiuto Informazioni sull'IVA in Europa .
- Come faccio a evitare la disattivazione dell'account?
- Per evitare la disattivazione dell'account, visita entro i prossimi 45 giorni la sezione relativa alle azioni prioritarie della pagina Stato dell'account . Da qui, potrai effettuare le seguenti operazioni:
-- Verificare le informazioni esistenti per i paesi in elenco</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6504,39 +6267,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6557,39 +6320,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6612,39 +6375,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6665,39 +6428,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6721,39 +6484,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6776,39 +6539,80 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions
+ 96
+ Starting May 5, 2026, we'll update the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, France, Italy and Spain stores.
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6826,39 +6630,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6888,39 +6692,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6936,39 +6740,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6984,109 +6788,6 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] Provide additional information within 45 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements you must provide us with a valid VAT Registration Number (‘VRN’) for all the countries in which we believe you have a VAT registration obligation or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway, and Switzerland in which you have VAT obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax Information Help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 45 days visit the Priority Actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit VAT information through Business Information and Tax Setting portals
-- Submit required documentation for extension or exemption requests
- What happens if I don’t provide th</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>[Action required] Provide additional information within 45 days to
- avoid account deactivation under European VAT registration requirements</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- We need you to provide additional information in order to comply with Amazon’s European Value Added Tax (VAT) registration requirements.
- Why is this happening?
- According to Amazon’s European VAT registration requirements, you must provide us with a valid VAT registration number (“VRN”) for all the countries in which we believe you have a VAT registration obligation, or confirmation of the Union One-Stop Shop (OSS) status for your home country.
- We identified VAT registration requirements for your account in the European Union, the United Kingdom, Norway and Switzerland in which you have Value Added Tax (VAT) obligation. Specifically, action may be required for the following:
- Poland
- To learn more, go to the European Value Added Tax information help page.
- How do I avoid account deactivation?
- To avoid account deactivation, within the next 45 days visit the Priority actions section on your Account Health page . From there, you will be able to:
-- Verify your existing information for listed countries
-- Submit Value Added Tax (VAT) information through business information and tax setting portals
-- Submit required documentation for extension or exemption request</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
